--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555564093</v>
+        <v>46157.93112852782</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112852782</v>
+        <v>46157.93136938869</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93136938869</v>
+        <v>46157.93384264455</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384264455</v>
+        <v>46157.93696052906</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696052906</v>
+        <v>46158.2820509037</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2820509037</v>
+        <v>46158.29652653897</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652653897</v>
+        <v>46158.29807870375</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807870375</v>
+        <v>46158.33370671</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370671</v>
+        <v>46158.37221908847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Декабрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221908847</v>
+        <v>46158.37275760845</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
